--- a/Filtered/HoustonClearLake.xlsx
+++ b/Filtered/HoustonClearLake.xlsx
@@ -574,6 +574,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -626,6 +636,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -698,6 +718,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -750,6 +780,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -822,6 +862,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -874,6 +924,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -946,6 +1006,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -998,6 +1068,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1070,6 +1150,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1122,6 +1212,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1194,6 +1294,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1266,6 +1376,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1318,6 +1438,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1390,6 +1520,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1442,6 +1582,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1499,6 +1649,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1551,6 +1711,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1623,6 +1793,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1675,6 +1855,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1732,6 +1922,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1784,6 +1984,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1856,6 +2066,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1908,6 +2128,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1980,6 +2210,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2032,6 +2272,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2104,6 +2354,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2156,6 +2416,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2228,6 +2498,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2280,6 +2560,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2352,6 +2642,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2404,6 +2704,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2476,6 +2786,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2528,6 +2848,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2585,6 +2915,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2637,6 +2977,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2709,6 +3059,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2761,6 +3121,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2833,6 +3203,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2885,6 +3265,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2957,6 +3347,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3009,6 +3409,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3081,6 +3491,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3133,6 +3553,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3205,6 +3635,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3257,6 +3697,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3329,6 +3779,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3381,6 +3841,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3453,6 +3923,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3505,6 +3985,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3577,6 +4067,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3629,6 +4129,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3701,6 +4211,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3753,6 +4273,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3825,6 +4355,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3877,6 +4417,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3949,6 +4499,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4001,6 +4561,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4073,6 +4643,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4125,6 +4705,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4182,6 +4772,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4234,6 +4834,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4306,6 +4916,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4358,6 +4978,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4430,6 +5060,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4482,6 +5122,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4554,6 +5204,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4606,6 +5266,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4678,6 +5348,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4730,6 +5410,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4802,6 +5492,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4854,6 +5554,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4926,6 +5636,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4978,6 +5698,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5050,6 +5780,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5102,6 +5842,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5174,6 +5924,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5226,6 +5986,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M78" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5298,6 +6068,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5350,6 +6130,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5422,6 +6212,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5474,6 +6274,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5546,6 +6356,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5598,6 +6418,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5670,6 +6500,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5722,6 +6562,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5794,6 +6644,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5846,6 +6706,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5918,6 +6788,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5970,6 +6850,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6042,6 +6932,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6094,6 +6994,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6166,6 +7076,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6218,6 +7138,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6290,6 +7220,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6342,6 +7282,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M96" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6414,6 +7364,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6466,6 +7426,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M98" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6538,6 +7508,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M99" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6590,6 +7570,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M100" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6662,6 +7652,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M101" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6714,6 +7714,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M102" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6786,6 +7796,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M103" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6838,6 +7858,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M104" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6910,6 +7940,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6962,6 +8002,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M106" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7034,6 +8084,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M107" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7106,6 +8166,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M108" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7158,6 +8228,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M109" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7230,6 +8310,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7302,6 +8392,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M111" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7354,6 +8454,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M112" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7426,6 +8536,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7478,6 +8598,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M114" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7550,6 +8680,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M115" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7622,6 +8762,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M116" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7674,6 +8824,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M117" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7746,6 +8906,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M118" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7798,6 +8968,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M119" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7870,6 +9050,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M120" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7942,6 +9132,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M121" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7994,6 +9194,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M122" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8066,6 +9276,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M123" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8118,6 +9338,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M124" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8190,6 +9420,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M125" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8242,6 +9482,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M126" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8314,6 +9564,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M127" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8366,6 +9626,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M128" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8423,6 +9693,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M129" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8475,6 +9755,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M130" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8532,6 +9822,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M131" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8589,6 +9889,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M132" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8641,6 +9951,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M133" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8713,6 +10033,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M134" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8765,6 +10095,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M135" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8837,6 +10177,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M136" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8889,6 +10239,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M137" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8961,6 +10321,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M138" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9013,6 +10383,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M139" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9085,6 +10465,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M140" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9137,6 +10527,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M141" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9209,6 +10609,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M142" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9261,6 +10671,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M143" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9333,6 +10753,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M144" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9385,6 +10815,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M145" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9457,6 +10897,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M146" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9509,6 +10959,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M147" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9581,6 +11041,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M148" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9633,6 +11103,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M149" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9705,6 +11185,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M150" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9757,6 +11247,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M151" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9829,6 +11329,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M152" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9881,6 +11391,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M153" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9953,6 +11473,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M154" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10005,6 +11535,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M155" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10077,6 +11617,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M156" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10129,6 +11679,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M157" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10201,6 +11761,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M158" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10253,6 +11823,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M159" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10325,6 +11905,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M160" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10377,6 +11967,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M161" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10449,6 +12049,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M162" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10521,6 +12131,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M163" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10573,6 +12193,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M164" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10630,6 +12260,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M165" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10682,6 +12322,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M166" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10754,6 +12404,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M167" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10806,6 +12466,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M168" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10878,6 +12548,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M169" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10930,6 +12610,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M170" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11002,6 +12692,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M171" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11054,6 +12754,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M172" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11126,6 +12836,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M173" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11178,6 +12898,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M174" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11250,6 +12980,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M175" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11302,6 +13042,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M176" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11374,6 +13124,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M177" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11426,6 +13186,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M178" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11498,6 +13268,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M179" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11550,6 +13330,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M180" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11622,6 +13412,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M181" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11674,6 +13474,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M182" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11746,6 +13556,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M183" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11798,6 +13618,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M184" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11870,6 +13700,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M185" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11922,6 +13762,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M186" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11994,6 +13844,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M187" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12046,6 +13906,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M188" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12118,6 +13988,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M189" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12170,6 +14050,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M190" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12242,6 +14132,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M191" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12294,6 +14194,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M192" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12366,6 +14276,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M193" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12418,6 +14338,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M194" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12475,6 +14405,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M195" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12532,6 +14472,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M196" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12589,6 +14539,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M197" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12641,6 +14601,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M198" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12713,6 +14683,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M199" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12765,6 +14745,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M200" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12837,6 +14827,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M201" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12889,6 +14889,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M202" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12961,6 +14971,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M203" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13013,6 +15033,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M204" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13085,6 +15115,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M205" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13137,6 +15177,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M206" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13209,6 +15259,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M207" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13261,6 +15321,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M208" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13333,6 +15403,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M209" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13385,6 +15465,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M210" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13457,6 +15547,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M211" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13509,6 +15609,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M212" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13581,6 +15691,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M213" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13633,6 +15753,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M214" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13705,6 +15835,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M215" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13757,6 +15897,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M216" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13829,6 +15979,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M217" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13881,6 +16041,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M218" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13953,6 +16123,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M219" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14005,6 +16185,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M220" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14077,6 +16267,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M221" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14129,6 +16329,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M222" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14201,6 +16411,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M223" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14253,6 +16473,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M224" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14325,6 +16555,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M225" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14377,6 +16617,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M226" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14449,6 +16699,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M227" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14501,6 +16761,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M228" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14573,6 +16843,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M229" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14625,6 +16905,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M230" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14697,6 +16987,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M231" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14749,6 +17049,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M232" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14821,6 +17131,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M233" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14873,6 +17193,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M234" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14945,6 +17275,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M235" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14997,6 +17337,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M236" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15054,6 +17404,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M237" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15106,6 +17466,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M238" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15178,6 +17548,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M239" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15230,6 +17610,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M240" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15287,6 +17677,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M241" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15339,6 +17739,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M242" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15411,6 +17821,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M243" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15463,6 +17883,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M244" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15535,6 +17965,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M245" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15587,6 +18027,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M246" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15659,6 +18109,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M247" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15711,6 +18171,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M248" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15783,6 +18253,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M249" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15835,6 +18315,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M250" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15907,6 +18397,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M251" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15959,6 +18459,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M252" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16031,6 +18541,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M253" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16103,6 +18623,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M254" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16155,6 +18685,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M255" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16212,6 +18752,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M256" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16264,6 +18814,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M257" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16336,6 +18896,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M258" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16388,6 +18958,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M259" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16460,6 +19040,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M260" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16512,6 +19102,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M261" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16584,6 +19184,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M262" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16636,6 +19246,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M263" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16708,6 +19328,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M264" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16760,6 +19390,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M265" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16832,6 +19472,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M266" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16884,6 +19534,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M267" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16956,6 +19616,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M268" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17008,6 +19678,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M269" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17080,6 +19760,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M270" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17132,6 +19822,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M271" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17204,6 +19904,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M272" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17256,6 +19966,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M273" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17328,6 +20048,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M274" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17380,6 +20110,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M275" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17452,6 +20192,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M276" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17504,6 +20254,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M277" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17576,6 +20336,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M278" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17628,6 +20398,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M279" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17700,6 +20480,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M280" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17752,6 +20542,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M281" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17824,6 +20624,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M282" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17876,6 +20686,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M283" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17948,6 +20768,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M284" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18000,6 +20830,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M285" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18072,6 +20912,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M286" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18124,6 +20974,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M287" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18196,6 +21056,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M288" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18248,6 +21118,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M289" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18320,6 +21200,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M290" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18372,6 +21262,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M291" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18444,6 +21344,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M292" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18496,6 +21406,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M293" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18568,6 +21488,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M294" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18620,6 +21550,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M295" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18692,6 +21632,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M296" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18744,6 +21694,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M297" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18816,6 +21776,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M298" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18868,6 +21838,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M299" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18940,6 +21920,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M300" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18992,6 +21982,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M301" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19064,6 +22064,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M302" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19116,6 +22126,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M303" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19188,6 +22208,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M304" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19240,6 +22270,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M305" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19312,6 +22352,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M306" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19364,6 +22414,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M307" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19436,6 +22496,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M308" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19488,6 +22558,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M309" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19560,6 +22640,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M310" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19612,6 +22702,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M311" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19684,6 +22784,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M312" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19736,6 +22846,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M313" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19808,6 +22928,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M314" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19860,6 +22990,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M315" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19932,6 +23072,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M316" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19984,6 +23134,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M317" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20056,6 +23216,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M318" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20108,6 +23278,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M319" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20180,6 +23360,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M320" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20252,6 +23442,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M321" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20304,6 +23504,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M322" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20376,6 +23586,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M323" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20428,6 +23648,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M324" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20500,6 +23730,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M325" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20552,6 +23792,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M326" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20624,6 +23874,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M327" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20676,6 +23936,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M328" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20748,6 +24018,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M329" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20800,6 +24080,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M330" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20872,6 +24162,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M331" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20924,6 +24224,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M332" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20996,6 +24306,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M333" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21048,6 +24368,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M334" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21120,6 +24450,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M335" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21172,6 +24512,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M336" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21244,6 +24594,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M337" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21296,6 +24656,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M338" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21363,6 +24733,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M339" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21415,6 +24795,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M340" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21487,6 +24877,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M341" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21559,6 +24959,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M342" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21611,6 +25021,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M343" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21683,6 +25103,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M344" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21735,6 +25165,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M345" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21807,6 +25247,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M346" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21859,6 +25309,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M347" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21931,6 +25391,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M348" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21983,6 +25453,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M349" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22040,6 +25520,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M350" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22092,6 +25582,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M351" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22164,6 +25664,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M352" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22216,6 +25726,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M353" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22288,6 +25808,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M354" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22340,6 +25870,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M355" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22412,6 +25952,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M356" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22464,6 +26014,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M357" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22521,6 +26081,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M358" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22573,6 +26143,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M359" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22645,6 +26225,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M360" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22697,6 +26287,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M361" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22769,6 +26369,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M362" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22821,6 +26431,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M363" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22893,6 +26513,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M364" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22945,6 +26575,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M365" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23002,6 +26642,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M366" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23054,6 +26704,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M367" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23126,6 +26786,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M368" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23178,6 +26848,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M369" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23250,6 +26930,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M370" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23302,6 +26992,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M371" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23374,6 +27074,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M372" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23426,6 +27136,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M373" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23498,6 +27218,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M374" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23550,6 +27280,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M375" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23622,6 +27362,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M376" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23674,6 +27424,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M377" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23746,6 +27506,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M378" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23798,6 +27568,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M379" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23870,6 +27650,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M380" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23942,6 +27732,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M381" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23994,6 +27794,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M382" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24066,6 +27876,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M383" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24118,6 +27938,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M384" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24190,6 +28020,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M385" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24242,6 +28082,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M386" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24314,6 +28164,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M387" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24366,6 +28226,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M388" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24438,6 +28308,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M389" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24490,6 +28370,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M390" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24562,6 +28452,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M391" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24614,6 +28514,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M392" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24671,6 +28581,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M393" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24723,6 +28643,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M394" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24795,6 +28725,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M395" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24847,6 +28787,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M396" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24919,6 +28869,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M397" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24971,6 +28931,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M398" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25043,6 +29013,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M399" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25095,6 +29075,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M400" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25167,6 +29157,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M401" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25219,6 +29219,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M402" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25291,6 +29301,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M403" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25343,6 +29363,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M404" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25415,6 +29445,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M405" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25467,6 +29507,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M406" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25539,6 +29589,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M407" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25591,6 +29651,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M408" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25663,6 +29733,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M409" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25715,6 +29795,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M410" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25787,6 +29877,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M411" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25839,6 +29939,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M412" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25911,6 +30021,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M413" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25983,6 +30103,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M414" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26035,6 +30165,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M415" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26107,6 +30247,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M416" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26159,6 +30309,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M417" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26231,6 +30391,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M418" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26283,6 +30453,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M419" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26355,6 +30535,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M420" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26407,6 +30597,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M421" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26479,6 +30679,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M422" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26531,6 +30741,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M423" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26603,6 +30823,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M424" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26655,6 +30885,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M425" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26727,6 +30967,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M426" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26779,6 +31029,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M427" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26851,6 +31111,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M428" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26903,6 +31173,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M429" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26975,6 +31255,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M430" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27027,6 +31317,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M431" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27084,6 +31384,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M432" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27141,6 +31451,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M433" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27198,6 +31518,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M434" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27250,6 +31580,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M435" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27322,6 +31662,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M436" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27374,6 +31724,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M437" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27431,6 +31791,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M438" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27488,6 +31858,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M439" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27545,6 +31925,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M440" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27602,6 +31992,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M441" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27659,6 +32059,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M442" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27711,6 +32121,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M443" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27783,6 +32203,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M444" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27835,6 +32265,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M445" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27907,6 +32347,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M446" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27959,6 +32409,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M447" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28016,6 +32476,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M448" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28073,6 +32543,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M449" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28130,6 +32610,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M450" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28182,6 +32672,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M451" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28254,6 +32754,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M452" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28306,6 +32816,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M453" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28363,6 +32883,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M454" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28420,6 +32950,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M455" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28477,6 +33017,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M456" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28529,6 +33079,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M457" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28601,6 +33161,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M458" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28653,6 +33223,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M459" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28725,6 +33305,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M460" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28777,6 +33367,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M461" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28834,6 +33434,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M462" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28886,6 +33496,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M463" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28958,6 +33578,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M464" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29010,6 +33640,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M465" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29082,6 +33722,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M466" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29134,6 +33784,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M467" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29191,6 +33851,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M468" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29248,6 +33918,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M469" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29305,6 +33985,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M470" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29357,6 +34047,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M471" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29414,6 +34114,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M472" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29471,6 +34181,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M473" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29523,6 +34243,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M474" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29580,6 +34310,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M475" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29637,6 +34377,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M476" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29694,6 +34444,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M477" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29746,6 +34506,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M478" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29818,6 +34588,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M479" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29870,6 +34650,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M480" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29927,6 +34717,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M481" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29984,6 +34784,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M482" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30036,6 +34846,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M483" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30093,6 +34913,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M484" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30150,6 +34980,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M485" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30207,6 +35047,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M486" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30259,6 +35109,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M487" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30331,6 +35191,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M488" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30383,6 +35253,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M489" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30440,6 +35320,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M490" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30492,6 +35382,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M491" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30564,6 +35464,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M492" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30616,6 +35526,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M493" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30673,6 +35593,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M494" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30730,6 +35660,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M495" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30787,6 +35727,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M496" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30839,6 +35789,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M497" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30911,6 +35871,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M498" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30963,6 +35933,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M499" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31035,6 +36015,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M500" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31087,6 +36077,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M501" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31144,6 +36144,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M502" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31201,6 +36211,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M503" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31253,6 +36273,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M504" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31310,6 +36340,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M505" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31360,6 +36400,16 @@
       <c r="J506" t="inlineStr">
         <is>
           <t>Acute</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>COCCL</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
         </is>
       </c>
       <c r="M506" t="inlineStr">
